--- a/assets/reaction_table.xlsx
+++ b/assets/reaction_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GodotProject\PotionProject\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93CBD7A-EDF3-4985-BA8E-F40D9BA050E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF864337-35BF-43DE-A67D-1EBE944EC2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="89">
   <si>
     <t>主体 ＼ 对象</t>
   </si>
@@ -148,9 +148,6 @@
     <t>耐力</t>
   </si>
   <si>
-    <t>等级+1</t>
-  </si>
-  <si>
     <t>治疗（等级+1）</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
     <t>荆棘（等级+1）</t>
   </si>
   <si>
-    <t>暴怒（等级+1）</t>
-  </si>
-  <si>
     <t>锋利（等级+1）</t>
   </si>
   <si>
@@ -190,7 +184,113 @@
     <t>裂伤（等级+1）</t>
   </si>
   <si>
-    <t>两者消失</t>
+    <t>力量</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>护己</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>裂伤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵消</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵巧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉重</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐力</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>迟缓</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>迅捷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>敏捷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>滞留</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵消</t>
+  </si>
+  <si>
+    <t>恢复（等级+1）</t>
+  </si>
+  <si>
+    <t>防御（等级+1）</t>
+  </si>
+  <si>
+    <t>强身+耐力</t>
+  </si>
+  <si>
+    <t>迟缓（等级+1）</t>
+  </si>
+  <si>
+    <t>爆炸（等级+1）</t>
+  </si>
+  <si>
+    <t>爆炸+中毒</t>
+  </si>
+  <si>
+    <t>中毒（等级-1）</t>
+  </si>
+  <si>
+    <t>中毒+虚弱</t>
+  </si>
+  <si>
+    <t>虚弱（等级+1）</t>
+  </si>
+  <si>
+    <t>易伤（等级+1）</t>
+  </si>
+  <si>
+    <t>滞留（等级+1）</t>
+  </si>
+  <si>
+    <t>雷（等级+1）</t>
+  </si>
+  <si>
+    <t>急速（等级+1）</t>
+  </si>
+  <si>
+    <t>冰（等级+1）</t>
+  </si>
+  <si>
+    <t>沉重（等级+1）</t>
+  </si>
+  <si>
+    <t>圣佑（等级+1）</t>
+  </si>
+  <si>
+    <t>耐力（等级+1）</t>
+  </si>
+  <si>
+    <t>冰</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣佑</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -198,183 +298,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>力量</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>净化</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>护己</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣佑</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级加一</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>易伤</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴怒</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>裂伤</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵消</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆炸升级</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆炸+中毒</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复加一</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵巧</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>治疗</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>固结</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>盐</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御升级</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>锋利</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>沉重</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>固结升级</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>荆棘</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>延时</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>耐力</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>虚弱</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>木质+木质</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>锋利加一</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>迟缓</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>迟缓+1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>火</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒-1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒+虚弱</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>迅捷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>敏捷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>水</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚弱+1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>吸血</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>易伤+1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>滞留</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>隐身</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>强身+耐力</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷+1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>急速</t>
+    <t>暴怒</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -837,297 +765,163 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AP42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="11" customWidth="1"/>
-    <col min="25" max="25" width="11" customWidth="1"/>
-    <col min="26" max="26" width="11" customWidth="1"/>
-    <col min="27" max="27" width="11" customWidth="1"/>
-    <col min="28" max="28" width="11" customWidth="1"/>
-    <col min="29" max="29" width="11" customWidth="1"/>
-    <col min="30" max="30" width="11" customWidth="1"/>
-    <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="32" width="11" customWidth="1"/>
-    <col min="33" max="33" width="11" customWidth="1"/>
-    <col min="34" max="34" width="11" customWidth="1"/>
-    <col min="35" max="35" width="11" customWidth="1"/>
-    <col min="36" max="36" width="11" customWidth="1"/>
-    <col min="37" max="37" width="11" customWidth="1"/>
-    <col min="38" max="38" width="11" customWidth="1"/>
-    <col min="39" max="39" width="11" customWidth="1"/>
-    <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="11" customWidth="1"/>
-    <col min="42" max="42" width="11" customWidth="1"/>
+    <col min="1" max="42" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主体 ＼ 对象</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">治疗</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">神圣</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">恢复</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">矿物</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">木质</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固结</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">隐身</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">护己</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迅捷</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">防御</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">力量</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">净化</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">荆棘</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">虚弱</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">易伤</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">吸血</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">强身</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">吸收</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">滞留</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雷</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暴怒</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">敏捷</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">灵巧</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">锋利</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">急速</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">裂伤</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">血肉</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">酸</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">盐</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">草本</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冰</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">沉重</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">圣佑</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">延时</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">耐力</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">治疗</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">治疗（等级+1）</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">净化</t>
-        </is>
+    <row r="1" spans="1:42" ht="25.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">恢复</t>
-        </is>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">抵消</t>
-        </is>
+      <c r="L2" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
@@ -1149,40 +943,40 @@
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
       <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
+      <c r="AG2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
+      <c r="AJ2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
       <c r="AO2" s="5"/>
       <c r="AP2" s="5"/>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">神圣</t>
-        </is>
+    <row r="3" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">净化</t>
-        </is>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">护己</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">圣佑</t>
-        </is>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -1191,7 +985,9 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="O3" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
@@ -1209,57 +1005,41 @@
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
       <c r="AF3" s="5"/>
-      <c r="AG3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">灵巧</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">强身</t>
-        </is>
+      <c r="AG3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
-      <c r="AK3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">护己</t>
-        </is>
-      </c>
+      <c r="AK3" s="3"/>
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
       <c r="AN3" s="5"/>
       <c r="AO3" s="5"/>
       <c r="AP3" s="5"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">恢复</t>
-        </is>
+    <row r="4" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">恢复（等级+1）</t>
-        </is>
+      <c r="D4" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">恢复（等级+1）</t>
-        </is>
+      <c r="F4" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">抵消</t>
-        </is>
+      <c r="L4" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1280,15 +1060,19 @@
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">治疗</t>
-        </is>
-      </c>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
+      <c r="AF4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
+      <c r="AJ4" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="AK4" s="5"/>
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
@@ -1296,47 +1080,35 @@
       <c r="AO4" s="5"/>
       <c r="AP4" s="5"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">矿物</t>
-        </is>
+    <row r="5" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">沉重</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固结</t>
-        </is>
+      <c r="E5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">锋利</t>
-        </is>
+      <c r="I5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="N5" s="5"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">防御（等级+1）</t>
-        </is>
-      </c>
+      <c r="O5" s="3"/>
       <c r="P5" s="5"/>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">盐</t>
-        </is>
+      <c r="Q5" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
@@ -1345,82 +1117,52 @@
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">盐</t>
-        </is>
-      </c>
+      <c r="Y5" s="3"/>
       <c r="Z5" s="5"/>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓</t>
-        </is>
+      <c r="AA5" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="AB5" s="5"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">锋利（等级+1）</t>
-        </is>
+      <c r="AC5" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="AD5" s="5"/>
       <c r="AE5" s="5"/>
       <c r="AF5" s="5"/>
-      <c r="AG5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">盐</t>
-        </is>
-      </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">力量</t>
-        </is>
-      </c>
-      <c r="AI5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒</t>
-        </is>
-      </c>
-      <c r="AJ5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">耐力</t>
-        </is>
-      </c>
-      <c r="AK5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">防御</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">滞留</t>
-        </is>
-      </c>
+      <c r="AG5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="3"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
       <c r="AO5" s="5"/>
       <c r="AP5" s="5"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">木质</t>
-        </is>
+    <row r="6" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固结（等级+1）</t>
-        </is>
-      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火（等级+1）</t>
-        </is>
+      <c r="I6" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -1434,17 +1176,13 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">强身+耐力</t>
-        </is>
+      <c r="V6" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火</t>
-        </is>
+      <c r="Y6" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z6" s="5"/>
       <c r="AA6" s="5"/>
@@ -1452,47 +1190,33 @@
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
-      <c r="AF6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">木质+木质</t>
-        </is>
-      </c>
-      <c r="AG6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">敏捷</t>
-        </is>
-      </c>
-      <c r="AH6" s="5"/>
-      <c r="AI6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">易伤</t>
-        </is>
-      </c>
-      <c r="AJ6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">延时</t>
-        </is>
-      </c>
-      <c r="AK6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">荆棘</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">延时</t>
-        </is>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="AM6" s="5"/>
       <c r="AN6" s="5"/>
       <c r="AO6" s="5"/>
       <c r="AP6" s="5"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">固结</t>
-        </is>
+    <row r="7" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1501,29 +1225,21 @@
       <c r="F7" s="5"/>
       <c r="G7" s="2"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">滞留</t>
-        </is>
+      <c r="I7" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓（等级+1）</t>
-        </is>
+      <c r="L7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">强身</t>
-        </is>
+      <c r="P7" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
@@ -1540,11 +1256,17 @@
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
+      <c r="AF7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG7" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="5"/>
+      <c r="AJ7" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="AK7" s="5"/>
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
@@ -1552,11 +1274,9 @@
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸</t>
-        </is>
+    <row r="8" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1564,33 +1284,27 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸（等级+1）</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸（等级+1）</t>
-        </is>
+      <c r="H8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">易伤</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暴怒</t>
-        </is>
+      <c r="O8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
+      <c r="R8" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
@@ -1605,38 +1319,28 @@
       <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
       <c r="AF8" s="5"/>
-      <c r="AG8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸（等级+1）</t>
-        </is>
+      <c r="AG8" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="AH8" s="5"/>
-      <c r="AI8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸+中毒</t>
-        </is>
-      </c>
-      <c r="AJ8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸（等级+1）</t>
-        </is>
+      <c r="AI8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="AK8" s="5"/>
-      <c r="AL8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">裂伤</t>
-        </is>
+      <c r="AL8" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火</t>
-        </is>
+    <row r="9" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1645,10 +1349,8 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火（等级+1）</t>
-        </is>
+      <c r="I9" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1656,10 +1358,8 @@
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暴怒</t>
-        </is>
+      <c r="P9" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
@@ -1669,10 +1369,8 @@
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸</t>
-        </is>
+      <c r="Y9" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
@@ -1680,43 +1378,33 @@
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5"/>
-      <c r="AF9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">抵消</t>
-        </is>
-      </c>
-      <c r="AG9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸</t>
-        </is>
-      </c>
-      <c r="AH9" s="5"/>
+      <c r="AF9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH9" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="AI9" s="5"/>
-      <c r="AJ9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">爆炸</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">盐</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水</t>
-        </is>
+      <c r="AJ9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="AM9" s="5"/>
       <c r="AN9" s="5"/>
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">隐身</t>
-        </is>
+    <row r="10" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1760,11 +1448,9 @@
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">护己</t>
-        </is>
+    <row r="11" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1808,11 +1494,9 @@
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒</t>
-        </is>
+    <row r="12" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1824,66 +1508,46 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒（等级+1）</t>
-        </is>
+      <c r="L12" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">裂伤</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">虚弱</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">治疗</t>
-        </is>
+      <c r="O12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">易伤</t>
-        </is>
+      <c r="V12" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
-      <c r="AA12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓</t>
-        </is>
+      <c r="AA12" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="AB12" s="5"/>
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
       <c r="AE12" s="5"/>
-      <c r="AF12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒（等级-1）</t>
-        </is>
+      <c r="AF12" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
-      <c r="AI12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒（等级+1）</t>
-        </is>
-      </c>
-      <c r="AJ12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒+虚弱</t>
-        </is>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="AK12" s="5"/>
       <c r="AL12" s="5"/>
@@ -1892,11 +1556,9 @@
       <c r="AO12" s="5"/>
       <c r="AP12" s="5"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓</t>
-        </is>
+    <row r="13" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1909,22 +1571,16 @@
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓（等级+1）</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">抵消</t>
-        </is>
+      <c r="M13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迅捷</t>
-        </is>
+      <c r="Q13" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
@@ -1946,21 +1602,17 @@
       <c r="AI13" s="5"/>
       <c r="AJ13" s="5"/>
       <c r="AK13" s="5"/>
-      <c r="AL13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冰</t>
-        </is>
+      <c r="AL13" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
       <c r="AO13" s="5"/>
       <c r="AP13" s="5"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迅捷</t>
-        </is>
+    <row r="14" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1974,10 +1626,8 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迅捷（等级+1）</t>
-        </is>
+      <c r="N14" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -1989,10 +1639,8 @@
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">灵巧</t>
-        </is>
+      <c r="Y14" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
@@ -2001,10 +1649,8 @@
       <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
       <c r="AF14" s="5"/>
-      <c r="AG14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迅捷（等级+1）</t>
-        </is>
+      <c r="AG14" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
@@ -2016,11 +1662,9 @@
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">防御</t>
-        </is>
+    <row r="15" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2035,10 +1679,8 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">防御（等级+1）</t>
-        </is>
+      <c r="O15" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
@@ -2059,24 +1701,22 @@
       <c r="AF15" s="5"/>
       <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
-      <c r="AI15" s="5"/>
+      <c r="AI15" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="AJ15" s="5"/>
       <c r="AK15" s="5"/>
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">吸收</t>
-        </is>
+      <c r="AN15" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="AO15" s="5"/>
       <c r="AP15" s="5"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">力量</t>
-        </is>
+    <row r="16" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2095,10 +1735,8 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">抵消</t>
-        </is>
+      <c r="S16" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -2124,11 +1762,9 @@
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">净化</t>
-        </is>
+    <row r="17" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -2147,15 +1783,11 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="5"/>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">力量</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">防御</t>
-        </is>
+      <c r="S17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
@@ -2171,10 +1803,8 @@
       <c r="AF17" s="5"/>
       <c r="AG17" s="5"/>
       <c r="AH17" s="5"/>
-      <c r="AI17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水</t>
-        </is>
+      <c r="AI17" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="AJ17" s="5"/>
       <c r="AK17" s="5"/>
@@ -2184,11 +1814,9 @@
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">荆棘</t>
-        </is>
+    <row r="18" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2206,10 +1834,8 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">荆棘（等级+1）</t>
-        </is>
+      <c r="R18" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
@@ -2236,11 +1862,9 @@
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">虚弱</t>
-        </is>
+    <row r="19" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -2259,10 +1883,8 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
-      <c r="S19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">虚弱（等级+1）</t>
-        </is>
+      <c r="S19" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2270,10 +1892,8 @@
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5"/>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">虚弱（等级+1）</t>
-        </is>
+      <c r="Z19" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="AA19" s="5"/>
       <c r="AB19" s="5"/>
@@ -2287,20 +1907,16 @@
       <c r="AJ19" s="5"/>
       <c r="AK19" s="5"/>
       <c r="AL19" s="5"/>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">虚弱（等级+1）</t>
-        </is>
+      <c r="AM19" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="AN19" s="5"/>
       <c r="AO19" s="5"/>
       <c r="AP19" s="5"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">易伤</t>
-        </is>
+    <row r="20" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2339,20 +1955,16 @@
       <c r="AJ20" s="5"/>
       <c r="AK20" s="5"/>
       <c r="AL20" s="5"/>
-      <c r="AM20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">易伤（等级+1）</t>
-        </is>
+      <c r="AM20" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="AN20" s="5"/>
       <c r="AO20" s="5"/>
       <c r="AP20" s="5"/>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">吸血</t>
-        </is>
+    <row r="21" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2373,10 +1985,8 @@
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">吸血（等级+1）</t>
-        </is>
+      <c r="U21" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="V21" s="5"/>
       <c r="W21" s="5"/>
@@ -2400,11 +2010,9 @@
       <c r="AO21" s="5"/>
       <c r="AP21" s="5"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">强身</t>
-        </is>
+    <row r="22" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2426,10 +2034,8 @@
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">强身（等级+1）</t>
-        </is>
+      <c r="V22" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
@@ -2446,25 +2052,19 @@
       <c r="AI22" s="5"/>
       <c r="AJ22" s="5"/>
       <c r="AK22" s="5"/>
-      <c r="AL22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">隐身</t>
-        </is>
+      <c r="AL22" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="AM22" s="5"/>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">吸血</t>
-        </is>
+      <c r="AN22" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">吸收</t>
-        </is>
+    <row r="23" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2508,11 +2108,9 @@
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">滞留</t>
-        </is>
+    <row r="24" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2536,10 +2134,8 @@
       <c r="U24" s="5"/>
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
-      <c r="X24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">滞留（等级+1）</t>
-        </is>
+      <c r="X24" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
@@ -2560,11 +2156,9 @@
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雷</t>
-        </is>
+    <row r="25" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2589,10 +2183,8 @@
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
-      <c r="Y25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雷（等级+1）</t>
-        </is>
+      <c r="Y25" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="Z25" s="5"/>
       <c r="AA25" s="5"/>
@@ -2600,43 +2192,33 @@
       <c r="AC25" s="5"/>
       <c r="AD25" s="5"/>
       <c r="AE25" s="5"/>
-      <c r="AF25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雷（等级+1）</t>
-        </is>
-      </c>
-      <c r="AG25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迅捷</t>
-        </is>
-      </c>
-      <c r="AH25" s="5"/>
+      <c r="AF25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH25" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="AI25" s="5"/>
-      <c r="AJ25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">灵巧</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">急速</t>
-        </is>
+      <c r="AJ25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL25" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暴怒</t>
-        </is>
+    <row r="26" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2680,11 +2262,9 @@
       <c r="AO26" s="5"/>
       <c r="AP26" s="5"/>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">敏捷</t>
-        </is>
+    <row r="27" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2711,20 +2291,16 @@
       <c r="X27" s="5"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
-      <c r="AA27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">敏捷（等级+1）</t>
-        </is>
+      <c r="AA27" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="AB27" s="5"/>
       <c r="AC27" s="5"/>
       <c r="AD27" s="5"/>
       <c r="AE27" s="5"/>
       <c r="AF27" s="5"/>
-      <c r="AG27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">急速</t>
-        </is>
+      <c r="AG27" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
@@ -2736,11 +2312,9 @@
       <c r="AO27" s="5"/>
       <c r="AP27" s="5"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">灵巧</t>
-        </is>
+    <row r="28" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2768,10 +2342,8 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
-      <c r="AB28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">灵巧（等级+1）</t>
-        </is>
+      <c r="AB28" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="AC28" s="5"/>
       <c r="AD28" s="5"/>
@@ -2786,17 +2358,13 @@
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
       <c r="AO28" s="5"/>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">灵巧（等级+1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">锋利</t>
-        </is>
+      <c r="AP28" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2825,10 +2393,8 @@
       <c r="Z29" s="5"/>
       <c r="AA29" s="5"/>
       <c r="AB29" s="5"/>
-      <c r="AC29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">锋利（等级+1）</t>
-        </is>
+      <c r="AC29" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="AD29" s="5"/>
       <c r="AE29" s="5"/>
@@ -2839,20 +2405,16 @@
       <c r="AJ29" s="5"/>
       <c r="AK29" s="5"/>
       <c r="AL29" s="5"/>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">裂伤</t>
-        </is>
+      <c r="AM29" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="AN29" s="5"/>
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">急速</t>
-        </is>
+    <row r="30" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2882,10 +2444,8 @@
       <c r="AA30" s="5"/>
       <c r="AB30" s="5"/>
       <c r="AC30" s="5"/>
-      <c r="AD30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">急速（等级+1）</t>
-        </is>
+      <c r="AD30" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="AE30" s="5"/>
       <c r="AF30" s="5"/>
@@ -2900,11 +2460,9 @@
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">裂伤</t>
-        </is>
+    <row r="31" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2935,10 +2493,8 @@
       <c r="AB31" s="5"/>
       <c r="AC31" s="5"/>
       <c r="AD31" s="5"/>
-      <c r="AE31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">裂伤（等级+1）</t>
-        </is>
+      <c r="AE31" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="AF31" s="5"/>
       <c r="AG31" s="5"/>
@@ -2952,11 +2508,9 @@
       <c r="AO31" s="5"/>
       <c r="AP31" s="5"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水</t>
-        </is>
+    <row r="32" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2991,36 +2545,26 @@
       <c r="AF32" s="2"/>
       <c r="AG32" s="5"/>
       <c r="AH32" s="5"/>
-      <c r="AI32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒</t>
-        </is>
-      </c>
-      <c r="AJ32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">净化</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">治疗</t>
-        </is>
-      </c>
-      <c r="AL32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冰</t>
-        </is>
+      <c r="AI32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL32" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AM32" s="5"/>
       <c r="AN32" s="5"/>
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风</t>
-        </is>
+    <row r="33" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3053,30 +2597,24 @@
       <c r="AD33" s="5"/>
       <c r="AE33" s="5"/>
       <c r="AF33" s="5"/>
-      <c r="AG33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迅捷</t>
-        </is>
+      <c r="AG33" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="AH33" s="5"/>
       <c r="AI33" s="5"/>
       <c r="AJ33" s="5"/>
       <c r="AK33" s="5"/>
-      <c r="AL33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓</t>
-        </is>
+      <c r="AL33" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="AM33" s="5"/>
       <c r="AN33" s="5"/>
       <c r="AO33" s="5"/>
       <c r="AP33" s="5"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">血肉</t>
-        </is>
+    <row r="34" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -3111,32 +2649,24 @@
       <c r="AF34" s="5"/>
       <c r="AG34" s="5"/>
       <c r="AH34" s="2"/>
-      <c r="AI34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒</t>
-        </is>
+      <c r="AI34" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AJ34" s="5"/>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">恢复</t>
-        </is>
-      </c>
-      <c r="AL34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">敏捷</t>
-        </is>
+      <c r="AK34" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL34" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AM34" s="5"/>
       <c r="AN34" s="5"/>
       <c r="AO34" s="5"/>
       <c r="AP34" s="5"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">酸</t>
-        </is>
+    <row r="35" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -3172,27 +2702,19 @@
       <c r="AG35" s="5"/>
       <c r="AH35" s="5"/>
       <c r="AI35" s="2"/>
-      <c r="AJ35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中毒</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">迟缓</t>
-        </is>
-      </c>
+      <c r="AJ35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">盐</t>
-        </is>
+    <row r="36" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3229,26 +2751,20 @@
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
       <c r="AJ36" s="2"/>
-      <c r="AK36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">力量</t>
-        </is>
-      </c>
-      <c r="AL36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水</t>
-        </is>
+      <c r="AK36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL36" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="AM36" s="5"/>
       <c r="AN36" s="5"/>
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">草本</t>
-        </is>
+    <row r="37" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3286,21 +2802,17 @@
       <c r="AI37" s="5"/>
       <c r="AJ37" s="5"/>
       <c r="AK37" s="2"/>
-      <c r="AL37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">滞留</t>
-        </is>
+      <c r="AL37" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冰</t>
-        </is>
+    <row r="38" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3338,21 +2850,17 @@
       <c r="AI38" s="5"/>
       <c r="AJ38" s="5"/>
       <c r="AK38" s="5"/>
-      <c r="AL38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冰（等级+1）</t>
-        </is>
+      <c r="AL38" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
       <c r="AO38" s="5"/>
       <c r="AP38" s="5"/>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">沉重</t>
-        </is>
+    <row r="39" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -3391,20 +2899,16 @@
       <c r="AJ39" s="5"/>
       <c r="AK39" s="5"/>
       <c r="AL39" s="5"/>
-      <c r="AM39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">沉重（等级+1）</t>
-        </is>
+      <c r="AM39" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="AN39" s="5"/>
       <c r="AO39" s="5"/>
       <c r="AP39" s="5"/>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">圣佑</t>
-        </is>
+    <row r="40" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3444,19 +2948,15 @@
       <c r="AK40" s="5"/>
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
-      <c r="AN40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">圣佑（等级+1）</t>
-        </is>
+      <c r="AN40" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="AO40" s="5"/>
       <c r="AP40" s="5"/>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">延时</t>
-        </is>
+    <row r="41" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3497,18 +2997,14 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
-      <c r="AO41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">延时（等级+1）</t>
-        </is>
+      <c r="AO41" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="AP41" s="5"/>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">耐力</t>
-        </is>
+    <row r="42" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -3550,12 +3046,12 @@
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
       <c r="AO42" s="5"/>
-      <c r="AP42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">耐力（等级+1）</t>
-        </is>
+      <c r="AP42" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/reaction_table.xlsx
+++ b/assets/reaction_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GodotProject\PotionProject\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF864337-35BF-43DE-A67D-1EBE944EC2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EC0F40-E2A4-4E89-841C-A5132D03E5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="80">
   <si>
     <t>主体 ＼ 对象</t>
   </si>
@@ -188,50 +188,14 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>恢复</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>护己</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>裂伤</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵消</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>灵巧</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>沉重</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>耐力</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>迟缓</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>迅捷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>敏捷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>滞留</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>抵消</t>
   </si>
   <si>
@@ -284,18 +248,6 @@
   </si>
   <si>
     <t>耐力（等级+1）</t>
-  </si>
-  <si>
-    <t>冰</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣佑</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>强身</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>虚弱</t>
@@ -303,6 +255,18 @@
   </si>
   <si>
     <t>暴怒</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>易伤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>急速</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>延时</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -921,7 +885,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
@@ -943,21 +907,21 @@
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
       <c r="AF2" s="5"/>
-      <c r="AG2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH2" s="5" t="s">
-        <v>54</v>
+      <c r="AG2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="AI2" s="5"/>
-      <c r="AJ2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL2" s="5" t="s">
-        <v>59</v>
+      <c r="AJ2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
@@ -974,7 +938,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="3"/>
+      <c r="F3" s="5"/>
       <c r="G3" s="3" t="s">
         <v>39</v>
       </c>
@@ -985,8 +949,8 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
-      <c r="O3" s="5" t="s">
-        <v>85</v>
+      <c r="O3" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
@@ -1006,14 +970,16 @@
       <c r="AE3" s="5"/>
       <c r="AF3" s="5"/>
       <c r="AG3" s="3" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI3" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AI3" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="AJ3" s="5"/>
-      <c r="AK3" s="3"/>
+      <c r="AK3" s="5"/>
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
       <c r="AN3" s="5"/>
@@ -1027,11 +993,11 @@
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -1039,7 +1005,7 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1063,15 +1029,15 @@
       <c r="AF4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="AG4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>86</v>
+      <c r="AG4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="AI4" s="5"/>
-      <c r="AJ4" s="5" t="s">
-        <v>65</v>
+      <c r="AJ4" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="AK4" s="5"/>
       <c r="AL4" s="5"/>
@@ -1101,11 +1067,11 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="5" t="s">
-        <v>60</v>
+      <c r="M5" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="N5" s="5"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="3" t="s">
         <v>35</v>
@@ -1117,7 +1083,7 @@
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
-      <c r="Y5" s="3"/>
+      <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
       <c r="AA5" s="3" t="s">
         <v>12</v>
@@ -1144,7 +1110,7 @@
       <c r="AK5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AL5" s="3"/>
+      <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
       <c r="AO5" s="5"/>
@@ -1159,7 +1125,7 @@
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="3" t="s">
         <v>43</v>
@@ -1177,7 +1143,7 @@
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
       <c r="V6" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
@@ -1190,12 +1156,12 @@
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
-      <c r="AF6" s="3"/>
+      <c r="AF6" s="5"/>
       <c r="AG6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AH6" s="5" t="s">
-        <v>87</v>
+      <c r="AH6" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="AI6" s="3" t="s">
         <v>12</v>
@@ -1234,7 +1200,7 @@
         <v>12</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -1256,16 +1222,16 @@
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
-      <c r="AF7" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG7" s="5" t="s">
-        <v>62</v>
+      <c r="AF7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="5" t="s">
-        <v>61</v>
+      <c r="AJ7" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="AK7" s="5"/>
       <c r="AL7" s="5"/>
@@ -1285,10 +1251,10 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1302,8 +1268,8 @@
         <v>25</v>
       </c>
       <c r="Q8" s="5"/>
-      <c r="R8" s="5" t="s">
-        <v>57</v>
+      <c r="R8" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
@@ -1320,14 +1286,14 @@
       <c r="AE8" s="5"/>
       <c r="AF8" s="5"/>
       <c r="AG8" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="AH8" s="5"/>
       <c r="AI8" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="AJ8" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="AK8" s="5"/>
       <c r="AL8" s="3" t="s">
@@ -1379,15 +1345,17 @@
       <c r="AD9" s="5"/>
       <c r="AE9" s="5"/>
       <c r="AF9" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AH9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI9" s="5"/>
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI9" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="AJ9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1541,13 +1509,13 @@
       <c r="AD12" s="5"/>
       <c r="AE12" s="5"/>
       <c r="AF12" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
-      <c r="AI12" s="3"/>
+      <c r="AI12" s="5"/>
       <c r="AJ12" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="AK12" s="5"/>
       <c r="AL12" s="5"/>
@@ -1572,10 +1540,10 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
@@ -1653,7 +1621,9 @@
         <v>46</v>
       </c>
       <c r="AH14" s="5"/>
-      <c r="AI14" s="5"/>
+      <c r="AI14" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="AJ14" s="5"/>
       <c r="AK14" s="5"/>
       <c r="AL14" s="5"/>
@@ -1680,7 +1650,7 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
@@ -1701,8 +1671,8 @@
       <c r="AF15" s="5"/>
       <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
-      <c r="AI15" s="5" t="s">
-        <v>58</v>
+      <c r="AI15" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="AJ15" s="5"/>
       <c r="AK15" s="5"/>
@@ -1736,7 +1706,7 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -1884,7 +1854,7 @@
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -1893,7 +1863,7 @@
       <c r="X19" s="5"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="AA19" s="5"/>
       <c r="AB19" s="5"/>
@@ -1908,7 +1878,7 @@
       <c r="AK19" s="5"/>
       <c r="AL19" s="5"/>
       <c r="AM19" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="AN19" s="5"/>
       <c r="AO19" s="5"/>
@@ -1956,7 +1926,7 @@
       <c r="AK20" s="5"/>
       <c r="AL20" s="5"/>
       <c r="AM20" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="AN20" s="5"/>
       <c r="AO20" s="5"/>
@@ -2135,7 +2105,7 @@
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
       <c r="X24" s="4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
@@ -2184,7 +2154,7 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="4" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="Z25" s="5"/>
       <c r="AA25" s="5"/>
@@ -2193,15 +2163,17 @@
       <c r="AD25" s="5"/>
       <c r="AE25" s="5"/>
       <c r="AF25" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AG25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AH25" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI25" s="5"/>
+      <c r="AH25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI25" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="AJ25" s="3" t="s">
         <v>27</v>
       </c>
@@ -2401,7 +2373,9 @@
       <c r="AF29" s="5"/>
       <c r="AG29" s="5"/>
       <c r="AH29" s="5"/>
-      <c r="AI29" s="5"/>
+      <c r="AI29" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="AJ29" s="5"/>
       <c r="AK29" s="5"/>
       <c r="AL29" s="5"/>
@@ -2445,7 +2419,7 @@
       <c r="AB30" s="5"/>
       <c r="AC30" s="5"/>
       <c r="AD30" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="AE30" s="5"/>
       <c r="AF30" s="5"/>
@@ -2601,8 +2575,12 @@
         <v>13</v>
       </c>
       <c r="AH33" s="5"/>
-      <c r="AI33" s="5"/>
-      <c r="AJ33" s="5"/>
+      <c r="AI33" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ33" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="AK33" s="5"/>
       <c r="AL33" s="3" t="s">
         <v>12</v>
@@ -2652,7 +2630,9 @@
       <c r="AI34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AJ34" s="5"/>
+      <c r="AJ34" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="AK34" s="3" t="s">
         <v>3</v>
       </c>
@@ -2705,7 +2685,7 @@
       <c r="AJ35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AK35" s="3"/>
+      <c r="AK35" s="5"/>
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
@@ -2851,7 +2831,7 @@
       <c r="AJ38" s="5"/>
       <c r="AK38" s="5"/>
       <c r="AL38" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
@@ -2900,7 +2880,7 @@
       <c r="AK39" s="5"/>
       <c r="AL39" s="5"/>
       <c r="AM39" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="AN39" s="5"/>
       <c r="AO39" s="5"/>
@@ -2949,7 +2929,7 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
       <c r="AN40" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AO40" s="5"/>
       <c r="AP40" s="5"/>
@@ -3047,7 +3027,7 @@
       <c r="AN42" s="5"/>
       <c r="AO42" s="5"/>
       <c r="AP42" s="4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
